--- a/Assets/Data/Tutorial.xlsx
+++ b/Assets/Data/Tutorial.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070"/>
+    <workbookView windowWidth="19200" windowHeight="7070" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Tutorial" sheetId="3" r:id="rId1"/>
@@ -210,8 +210,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -224,14 +224,47 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -245,7 +278,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -260,15 +301,29 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -289,71 +344,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -366,6 +359,13 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -376,37 +376,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -418,145 +550,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -570,41 +570,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -633,11 +603,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -675,7 +675,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -684,7 +684,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -693,127 +693,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Tutorial.xlsx
+++ b/Assets/Data/Tutorial.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7070"/>
   </bookViews>
   <sheets>
     <sheet name="Tutorial" sheetId="3" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="54">
   <si>
     <t>Id</t>
   </si>
@@ -202,6 +202,26 @@
     <t>■バトル評価値
 バトル勝利時に獲得したバトル評価の累積値です。
 この値が高いとバトル勝利時に獲得する(Nu)にボーナス補正が入ります。</t>
+  </si>
+  <si>
+    <t>作戦設定</t>
+  </si>
+  <si>
+    <t>■作戦設定
+キャラクターがバトルで使用する魔法を
+ステータス画面の作戦設定で変えることができます。</t>
+  </si>
+  <si>
+    <t>■作戦設定
+キャラクター毎にバトル中の行動を設定します。
+作戦は魔法毎に優先順位と2つまで条件を設定できます。
+キャラクターは優先順位の高い方から使用可能になった魔法を選択します。</t>
+  </si>
+  <si>
+    <t>■作戦設定
+Acitve・Awaken魔法は作戦に設定しなければ使用しません。
+Passive・Unique魔法は作戦に設定しなくても発動しますが
+条件を設定した時は条件に一致する場合にのみ効果を発動します。</t>
   </si>
 </sst>
 </file>
@@ -209,10 +229,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -223,8 +243,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -238,6 +274,35 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -247,15 +312,15 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -271,37 +336,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,21 +352,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -338,15 +366,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -359,13 +386,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -376,19 +396,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -400,163 +576,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,46 +594,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -636,8 +617,38 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -659,6 +670,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -675,151 +695,154 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1146,7 +1169,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -1155,34 +1178,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
@@ -2163,6 +2186,138 @@
         <v>540</v>
       </c>
       <c r="N23">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24">
+        <v>11000</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>1200</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>504</v>
+      </c>
+      <c r="H24">
+        <v>-272</v>
+      </c>
+      <c r="I24">
+        <v>184</v>
+      </c>
+      <c r="J24">
+        <v>72</v>
+      </c>
+      <c r="K24">
+        <v>320</v>
+      </c>
+      <c r="L24">
+        <v>-160</v>
+      </c>
+      <c r="M24">
+        <v>540</v>
+      </c>
+      <c r="N24">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25">
+        <v>11010</v>
+      </c>
+      <c r="B25">
+        <v>200</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>1200</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>504</v>
+      </c>
+      <c r="H25">
+        <v>-272</v>
+      </c>
+      <c r="I25">
+        <v>184</v>
+      </c>
+      <c r="J25">
+        <v>72</v>
+      </c>
+      <c r="K25">
+        <v>320</v>
+      </c>
+      <c r="L25">
+        <v>-136</v>
+      </c>
+      <c r="M25">
+        <v>620</v>
+      </c>
+      <c r="N25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26">
+        <v>11020</v>
+      </c>
+      <c r="B26">
+        <v>111</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26">
+        <v>1200</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>156</v>
+      </c>
+      <c r="I26">
+        <v>1080</v>
+      </c>
+      <c r="J26">
+        <v>256</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>-56</v>
+      </c>
+      <c r="M26">
+        <v>648</v>
+      </c>
+      <c r="N26">
         <v>144</v>
       </c>
     </row>
@@ -2175,7 +2330,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="18.8181818181818" customWidth="1"/>
@@ -2435,6 +2590,39 @@
         <v>49</v>
       </c>
     </row>
+    <row r="24" ht="39" spans="1:3">
+      <c r="A24">
+        <v>11000</v>
+      </c>
+      <c r="B24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" ht="65" spans="1:3">
+      <c r="A25">
+        <v>11010</v>
+      </c>
+      <c r="B25" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" ht="52" spans="1:3">
+      <c r="A26">
+        <v>11020</v>
+      </c>
+      <c r="B26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
